--- a/data/stocks/EUStocks.xlsx
+++ b/data/stocks/EUStocks.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:J26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -470,6 +470,11 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>Z-Score</t>
         </is>
       </c>
@@ -495,7 +500,10 @@
       <c r="H2" t="n">
         <v>1000</v>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="n">
+        <v>2000</v>
+      </c>
+      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -523,6 +531,9 @@
         <v>1003.46</v>
       </c>
       <c r="I3" t="n">
+        <v>2001</v>
+      </c>
+      <c r="J3" t="n">
         <v>-1.294075304597541</v>
       </c>
     </row>
@@ -552,6 +563,9 @@
         <v>817.9400000000001</v>
       </c>
       <c r="I4" t="n">
+        <v>2002</v>
+      </c>
+      <c r="J4" t="n">
         <v>-2.192341079997108</v>
       </c>
     </row>
@@ -581,6 +595,9 @@
         <v>620.71</v>
       </c>
       <c r="I5" t="n">
+        <v>2003</v>
+      </c>
+      <c r="J5" t="n">
         <v>0.7068711748633327</v>
       </c>
     </row>
@@ -610,6 +627,9 @@
         <v>684.71</v>
       </c>
       <c r="I6" t="n">
+        <v>2004</v>
+      </c>
+      <c r="J6" t="n">
         <v>0.2419264401156756</v>
       </c>
     </row>
@@ -639,6 +659,9 @@
         <v>865.3</v>
       </c>
       <c r="I7" t="n">
+        <v>2005</v>
+      </c>
+      <c r="J7" t="n">
         <v>1.042169695933184</v>
       </c>
     </row>
@@ -668,6 +691,9 @@
         <v>1023.14</v>
       </c>
       <c r="I8" t="n">
+        <v>2006</v>
+      </c>
+      <c r="J8" t="n">
         <v>0.7046222424441962</v>
       </c>
     </row>
@@ -697,6 +723,9 @@
         <v>1157.61</v>
       </c>
       <c r="I9" t="n">
+        <v>2007</v>
+      </c>
+      <c r="J9" t="n">
         <v>0.2551237409081213</v>
       </c>
     </row>
@@ -726,6 +755,9 @@
         <v>1108.72</v>
       </c>
       <c r="I10" t="n">
+        <v>2008</v>
+      </c>
+      <c r="J10" t="n">
         <v>-2.515505214664362</v>
       </c>
     </row>
@@ -755,6 +787,9 @@
         <v>838.35</v>
       </c>
       <c r="I11" t="n">
+        <v>2009</v>
+      </c>
+      <c r="J11" t="n">
         <v>1.139537757459768</v>
       </c>
     </row>
@@ -784,6 +819,9 @@
         <v>850.8</v>
       </c>
       <c r="I12" t="n">
+        <v>2010</v>
+      </c>
+      <c r="J12" t="n">
         <v>-0.3979131754046606</v>
       </c>
     </row>
@@ -813,6 +851,9 @@
         <v>900.73</v>
       </c>
       <c r="I13" t="n">
+        <v>2011</v>
+      </c>
+      <c r="J13" t="n">
         <v>-0.9948901136392033</v>
       </c>
     </row>
@@ -842,6 +883,9 @@
         <v>856.9</v>
       </c>
       <c r="I14" t="n">
+        <v>2012</v>
+      </c>
+      <c r="J14" t="n">
         <v>0.7412718125689417</v>
       </c>
     </row>
@@ -871,6 +915,9 @@
         <v>1041.41</v>
       </c>
       <c r="I15" t="n">
+        <v>2013</v>
+      </c>
+      <c r="J15" t="n">
         <v>0.909208837143494</v>
       </c>
     </row>
@@ -900,6 +947,9 @@
         <v>1141.58</v>
       </c>
       <c r="I16" t="n">
+        <v>2014</v>
+      </c>
+      <c r="J16" t="n">
         <v>-0.03523164086150139</v>
       </c>
     </row>
@@ -929,6 +979,9 @@
         <v>1335.35</v>
       </c>
       <c r="I17" t="n">
+        <v>2015</v>
+      </c>
+      <c r="J17" t="n">
         <v>0.08934838878634917</v>
       </c>
     </row>
@@ -958,6 +1011,9 @@
         <v>1225.03</v>
       </c>
       <c r="I18" t="n">
+        <v>2016</v>
+      </c>
+      <c r="J18" t="n">
         <v>-0.04573590520756658</v>
       </c>
     </row>
@@ -987,6 +1043,9 @@
         <v>1423.72</v>
       </c>
       <c r="I19" t="n">
+        <v>2017</v>
+      </c>
+      <c r="J19" t="n">
         <v>0.2361008348504622</v>
       </c>
     </row>
@@ -1016,6 +1075,9 @@
         <v>1419.56</v>
       </c>
       <c r="I20" t="n">
+        <v>2018</v>
+      </c>
+      <c r="J20" t="n">
         <v>-0.8937835684963534</v>
       </c>
     </row>
@@ -1045,6 +1107,9 @@
         <v>1567.61</v>
       </c>
       <c r="I21" t="n">
+        <v>2019</v>
+      </c>
+      <c r="J21" t="n">
         <v>1.257517899414159</v>
       </c>
     </row>
@@ -1074,6 +1139,9 @@
         <v>1602.32</v>
       </c>
       <c r="I22" t="n">
+        <v>2020</v>
+      </c>
+      <c r="J22" t="n">
         <v>-0.4344642318556678</v>
       </c>
     </row>
@@ -1103,6 +1171,9 @@
         <v>1918.65</v>
       </c>
       <c r="I23" t="n">
+        <v>2021</v>
+      </c>
+      <c r="J23" t="n">
         <v>0.9798408716860909</v>
       </c>
     </row>
@@ -1132,6 +1203,9 @@
         <v>1913.01</v>
       </c>
       <c r="I24" t="n">
+        <v>2022</v>
+      </c>
+      <c r="J24" t="n">
         <v>-0.7651697417667866</v>
       </c>
     </row>
@@ -1161,6 +1235,9 @@
         <v>2133.06</v>
       </c>
       <c r="I25" t="n">
+        <v>2023</v>
+      </c>
+      <c r="J25" t="n">
         <v>0.9328612010525258</v>
       </c>
     </row>
@@ -1190,6 +1267,9 @@
         <v>2424.75</v>
       </c>
       <c r="I26" t="n">
+        <v>2024</v>
+      </c>
+      <c r="J26" t="n">
         <v>0.3327090792644502</v>
       </c>
     </row>

--- a/data/stocks/EUStocks.xlsx
+++ b/data/stocks/EUStocks.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -475,802 +475,783 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>Log_return</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>Z-Score</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>36891</v>
+        <v>37256</v>
       </c>
       <c r="C2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+        <v>812.0599999999999</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-187.94</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-0.18794</v>
+      </c>
       <c r="F2" t="n">
-        <v>1000</v>
+        <v>985.3</v>
       </c>
       <c r="G2" t="n">
-        <v>1000</v>
+        <v>613.58</v>
       </c>
       <c r="H2" t="n">
-        <v>1000</v>
+        <v>1003.46</v>
       </c>
       <c r="I2" t="n">
-        <v>2000</v>
-      </c>
-      <c r="J2" t="inlineStr"/>
+        <v>2001</v>
+      </c>
+      <c r="J2" t="n">
+        <v>-0.2082</v>
+      </c>
+      <c r="K2" t="n">
+        <v>-2.023246540648724</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>37256</v>
+        <v>37986</v>
       </c>
       <c r="C3" t="n">
-        <v>812.0599999999999</v>
+        <v>620.71</v>
       </c>
       <c r="D3" t="n">
-        <v>-187.94</v>
+        <v>98.76000000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.18794</v>
+        <v>0.189213526199828</v>
       </c>
       <c r="F3" t="n">
-        <v>985.3</v>
+        <v>551.78</v>
       </c>
       <c r="G3" t="n">
-        <v>613.58</v>
+        <v>405.23</v>
       </c>
       <c r="H3" t="n">
-        <v>1003.46</v>
+        <v>620.71</v>
       </c>
       <c r="I3" t="n">
-        <v>2001</v>
+        <v>2003</v>
       </c>
       <c r="J3" t="n">
-        <v>-1.294075304597541</v>
+        <v>0.1733</v>
+      </c>
+      <c r="K3" t="n">
+        <v>-0.1482774952237081</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>37621</v>
+        <v>38352</v>
       </c>
       <c r="C4" t="n">
-        <v>521.95</v>
+        <v>683.76</v>
       </c>
       <c r="D4" t="n">
-        <v>-290.11</v>
+        <v>63.05</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.357251927197498</v>
+        <v>0.101577226079812</v>
       </c>
       <c r="F4" t="n">
-        <v>801.39</v>
+        <v>629.22</v>
       </c>
       <c r="G4" t="n">
-        <v>469.48</v>
+        <v>596.5</v>
       </c>
       <c r="H4" t="n">
-        <v>817.9400000000001</v>
+        <v>684.71</v>
       </c>
       <c r="I4" t="n">
-        <v>2002</v>
+        <v>2004</v>
       </c>
       <c r="J4" t="n">
-        <v>-2.192341079997108</v>
+        <v>0.09669999999999999</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-0.5247457229551794</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>37986</v>
+        <v>38717</v>
       </c>
       <c r="C5" t="n">
-        <v>620.71</v>
+        <v>856.35</v>
       </c>
       <c r="D5" t="n">
-        <v>98.76000000000001</v>
+        <v>172.59</v>
       </c>
       <c r="E5" t="n">
-        <v>0.189213526199828</v>
+        <v>0.252413127413127</v>
       </c>
       <c r="F5" t="n">
-        <v>551.78</v>
+        <v>688.4</v>
       </c>
       <c r="G5" t="n">
-        <v>405.23</v>
+        <v>677.98</v>
       </c>
       <c r="H5" t="n">
-        <v>620.71</v>
+        <v>865.3</v>
       </c>
       <c r="I5" t="n">
-        <v>2003</v>
+        <v>2005</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7068711748633327</v>
+        <v>0.2251</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.106305457733083</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>38352</v>
+        <v>39082</v>
       </c>
       <c r="C6" t="n">
-        <v>683.76</v>
+        <v>1018.02</v>
       </c>
       <c r="D6" t="n">
-        <v>63.05</v>
+        <v>161.67</v>
       </c>
       <c r="E6" t="n">
-        <v>0.101577226079812</v>
+        <v>0.188789630408127</v>
       </c>
       <c r="F6" t="n">
-        <v>629.22</v>
+        <v>862.7</v>
       </c>
       <c r="G6" t="n">
-        <v>596.5</v>
+        <v>834.4</v>
       </c>
       <c r="H6" t="n">
-        <v>684.71</v>
+        <v>1023.14</v>
       </c>
       <c r="I6" t="n">
-        <v>2004</v>
+        <v>2006</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2419264401156756</v>
+        <v>0.1729</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-0.150243386752332</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>38717</v>
+        <v>39447</v>
       </c>
       <c r="C7" t="n">
-        <v>856.35</v>
+        <v>1123.96</v>
       </c>
       <c r="D7" t="n">
-        <v>172.59</v>
+        <v>105.94</v>
       </c>
       <c r="E7" t="n">
-        <v>0.252413127413127</v>
+        <v>0.104064753148268</v>
       </c>
       <c r="F7" t="n">
-        <v>688.4</v>
+        <v>1033.7</v>
       </c>
       <c r="G7" t="n">
-        <v>677.98</v>
+        <v>966.86</v>
       </c>
       <c r="H7" t="n">
-        <v>865.3</v>
+        <v>1157.61</v>
       </c>
       <c r="I7" t="n">
-        <v>2005</v>
+        <v>2007</v>
       </c>
       <c r="J7" t="n">
-        <v>1.042169695933184</v>
+        <v>0.099</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-0.513441846665592</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>39082</v>
+        <v>40178</v>
       </c>
       <c r="C8" t="n">
-        <v>1018.02</v>
+        <v>831.03</v>
       </c>
       <c r="D8" t="n">
-        <v>161.67</v>
+        <v>177.07</v>
       </c>
       <c r="E8" t="n">
-        <v>0.188789630408127</v>
+        <v>0.270765796073154</v>
       </c>
       <c r="F8" t="n">
-        <v>862.7</v>
+        <v>677.98</v>
       </c>
       <c r="G8" t="n">
-        <v>834.4</v>
+        <v>485.2</v>
       </c>
       <c r="H8" t="n">
-        <v>1023.14</v>
+        <v>838.35</v>
       </c>
       <c r="I8" t="n">
-        <v>2006</v>
+        <v>2009</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7046222424441962</v>
+        <v>0.2396</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.1775690256456984</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>39447</v>
+        <v>40543</v>
       </c>
       <c r="C9" t="n">
-        <v>1123.96</v>
+        <v>815.22</v>
       </c>
       <c r="D9" t="n">
-        <v>105.94</v>
+        <v>-15.8099999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>0.104064753148268</v>
+        <v>-0.0190245839500378</v>
       </c>
       <c r="F9" t="n">
-        <v>1033.7</v>
+        <v>845.84</v>
       </c>
       <c r="G9" t="n">
-        <v>966.86</v>
+        <v>703.9400000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>1157.61</v>
+        <v>850.8</v>
       </c>
       <c r="I9" t="n">
-        <v>2007</v>
+        <v>2010</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2551237409081213</v>
+        <v>-0.0192</v>
+      </c>
+      <c r="K9" t="n">
+        <v>-1.094362793373946</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>39813</v>
+        <v>40908</v>
       </c>
       <c r="C10" t="n">
-        <v>653.96</v>
+        <v>707.98</v>
       </c>
       <c r="D10" t="n">
-        <v>-470</v>
+        <v>-107.24</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.418164347485676</v>
+        <v>-0.131547312381934</v>
       </c>
       <c r="F10" t="n">
-        <v>1108.72</v>
+        <v>819.58</v>
       </c>
       <c r="G10" t="n">
-        <v>577.46</v>
+        <v>587.71</v>
       </c>
       <c r="H10" t="n">
-        <v>1108.72</v>
+        <v>900.73</v>
       </c>
       <c r="I10" t="n">
-        <v>2008</v>
+        <v>2011</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.515505214664362</v>
+        <v>-0.141</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-1.692976763839914</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>40178</v>
+        <v>41274</v>
       </c>
       <c r="C11" t="n">
-        <v>831.03</v>
+        <v>846.53</v>
       </c>
       <c r="D11" t="n">
-        <v>177.07</v>
+        <v>138.55</v>
       </c>
       <c r="E11" t="n">
-        <v>0.270765796073154</v>
+        <v>0.195697618576796</v>
       </c>
       <c r="F11" t="n">
-        <v>677.98</v>
+        <v>707.73</v>
       </c>
       <c r="G11" t="n">
-        <v>485.2</v>
+        <v>649.6</v>
       </c>
       <c r="H11" t="n">
-        <v>838.35</v>
+        <v>856.9</v>
       </c>
       <c r="I11" t="n">
-        <v>2009</v>
+        <v>2012</v>
       </c>
       <c r="J11" t="n">
-        <v>1.139537757459768</v>
+        <v>0.1787</v>
+      </c>
+      <c r="K11" t="n">
+        <v>-0.1217379595872859</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>40543</v>
+        <v>41639</v>
       </c>
       <c r="C12" t="n">
-        <v>815.22</v>
+        <v>1038.99</v>
       </c>
       <c r="D12" t="n">
-        <v>-15.8099999999999</v>
+        <v>192.46</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.0190245839500378</v>
+        <v>0.227351659126079</v>
       </c>
       <c r="F12" t="n">
-        <v>845.84</v>
+        <v>854.1900000000001</v>
       </c>
       <c r="G12" t="n">
-        <v>703.9400000000001</v>
+        <v>822.3200000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>850.8</v>
+        <v>1041.41</v>
       </c>
       <c r="I12" t="n">
-        <v>2010</v>
+        <v>2013</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.3979131754046606</v>
+        <v>0.2049</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.007027935537577605</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>40908</v>
+        <v>42004</v>
       </c>
       <c r="C13" t="n">
-        <v>707.98</v>
+        <v>1090.25</v>
       </c>
       <c r="D13" t="n">
-        <v>-107.24</v>
+        <v>51.26</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.131547312381934</v>
+        <v>0.0493363747485539</v>
       </c>
       <c r="F13" t="n">
-        <v>819.58</v>
+        <v>1041.45</v>
       </c>
       <c r="G13" t="n">
-        <v>587.71</v>
+        <v>962.36</v>
       </c>
       <c r="H13" t="n">
-        <v>900.73</v>
+        <v>1141.58</v>
       </c>
       <c r="I13" t="n">
-        <v>2011</v>
+        <v>2014</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.9948901136392033</v>
+        <v>0.0482</v>
+      </c>
+      <c r="K13" t="n">
+        <v>-0.7631100708008236</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>41274</v>
+        <v>42369</v>
       </c>
       <c r="C14" t="n">
-        <v>846.53</v>
+        <v>1169.64</v>
       </c>
       <c r="D14" t="n">
-        <v>138.55</v>
+        <v>79.3900000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>0.195697618576796</v>
+        <v>0.0728181609722542</v>
       </c>
       <c r="F14" t="n">
-        <v>707.73</v>
+        <v>1098.33</v>
       </c>
       <c r="G14" t="n">
-        <v>649.6</v>
+        <v>1039.01</v>
       </c>
       <c r="H14" t="n">
-        <v>856.9</v>
+        <v>1335.35</v>
       </c>
       <c r="I14" t="n">
-        <v>2012</v>
+        <v>2015</v>
       </c>
       <c r="J14" t="n">
-        <v>0.7412718125689417</v>
+        <v>0.0703</v>
+      </c>
+      <c r="K14" t="n">
+        <v>-0.6544945638443548</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>41639</v>
+        <v>42735</v>
       </c>
       <c r="C15" t="n">
-        <v>1038.99</v>
+        <v>1225.03</v>
       </c>
       <c r="D15" t="n">
-        <v>192.46</v>
+        <v>55.3899999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>0.227351659126079</v>
+        <v>0.0473564515577442</v>
       </c>
       <c r="F15" t="n">
-        <v>854.1900000000001</v>
+        <v>1169.1</v>
       </c>
       <c r="G15" t="n">
-        <v>822.3200000000001</v>
+        <v>959.22</v>
       </c>
       <c r="H15" t="n">
-        <v>1041.41</v>
+        <v>1225.03</v>
       </c>
       <c r="I15" t="n">
-        <v>2013</v>
+        <v>2016</v>
       </c>
       <c r="J15" t="n">
-        <v>0.909208837143494</v>
+        <v>0.0463</v>
+      </c>
+      <c r="K15" t="n">
+        <v>-0.772448055561787</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>42004</v>
+        <v>43100</v>
       </c>
       <c r="C16" t="n">
-        <v>1090.25</v>
+        <v>1348.12</v>
       </c>
       <c r="D16" t="n">
-        <v>51.26</v>
+        <v>123.09</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0493363747485539</v>
+        <v>0.100479171938646</v>
       </c>
       <c r="F16" t="n">
-        <v>1041.45</v>
+        <v>1220.69</v>
       </c>
       <c r="G16" t="n">
-        <v>962.36</v>
+        <v>1199.84</v>
       </c>
       <c r="H16" t="n">
-        <v>1141.58</v>
+        <v>1423.72</v>
       </c>
       <c r="I16" t="n">
-        <v>2014</v>
+        <v>2017</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.03523164086150139</v>
+        <v>0.09569999999999999</v>
+      </c>
+      <c r="K16" t="n">
+        <v>-0.529660451776739</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>42369</v>
+        <v>43465</v>
       </c>
       <c r="C17" t="n">
-        <v>1169.64</v>
+        <v>1196.47</v>
       </c>
       <c r="D17" t="n">
-        <v>79.3900000000001</v>
+        <v>-151.65</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0728181609722542</v>
+        <v>-0.112489986054654</v>
       </c>
       <c r="F17" t="n">
-        <v>1098.33</v>
+        <v>1349.1</v>
       </c>
       <c r="G17" t="n">
-        <v>1039.01</v>
+        <v>1159.51</v>
       </c>
       <c r="H17" t="n">
-        <v>1335.35</v>
+        <v>1419.56</v>
       </c>
       <c r="I17" t="n">
-        <v>2015</v>
+        <v>2018</v>
       </c>
       <c r="J17" t="n">
-        <v>0.08934838878634917</v>
+        <v>-0.1193</v>
+      </c>
+      <c r="K17" t="n">
+        <v>-1.586327148412069</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>42735</v>
+        <v>43830</v>
       </c>
       <c r="C18" t="n">
-        <v>1225.03</v>
+        <v>1547.04</v>
       </c>
       <c r="D18" t="n">
-        <v>55.3899999999999</v>
+        <v>350.57</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0473564515577442</v>
+        <v>0.293003585547485</v>
       </c>
       <c r="F18" t="n">
-        <v>1169.1</v>
+        <v>1189.04</v>
       </c>
       <c r="G18" t="n">
-        <v>959.22</v>
+        <v>1170.69</v>
       </c>
       <c r="H18" t="n">
-        <v>1225.03</v>
+        <v>1567.61</v>
       </c>
       <c r="I18" t="n">
-        <v>2016</v>
+        <v>2019</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.04573590520756658</v>
+        <v>0.257</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.2630853071408368</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>43100</v>
+        <v>44196</v>
       </c>
       <c r="C19" t="n">
-        <v>1348.12</v>
+        <v>1506.95</v>
       </c>
       <c r="D19" t="n">
-        <v>123.09</v>
+        <v>-40.0899999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>0.100479171938646</v>
+        <v>-0.0259140035163925</v>
       </c>
       <c r="F19" t="n">
-        <v>1220.69</v>
+        <v>1550.8</v>
       </c>
       <c r="G19" t="n">
-        <v>1199.84</v>
+        <v>954.55</v>
       </c>
       <c r="H19" t="n">
-        <v>1423.72</v>
+        <v>1602.32</v>
       </c>
       <c r="I19" t="n">
-        <v>2017</v>
+        <v>2020</v>
       </c>
       <c r="J19" t="n">
-        <v>0.2361008348504622</v>
+        <v>-0.0263</v>
+      </c>
+      <c r="K19" t="n">
+        <v>-1.129257368007019</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>43465</v>
+        <v>44561</v>
       </c>
       <c r="C20" t="n">
-        <v>1196.47</v>
+        <v>1869.62</v>
       </c>
       <c r="D20" t="n">
-        <v>-151.65</v>
+        <v>362.67</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.112489986054654</v>
+        <v>0.240664919207671</v>
       </c>
       <c r="F20" t="n">
-        <v>1349.1</v>
+        <v>1513.51</v>
       </c>
       <c r="G20" t="n">
-        <v>1159.51</v>
+        <v>1475.91</v>
       </c>
       <c r="H20" t="n">
-        <v>1419.56</v>
+        <v>1918.65</v>
       </c>
       <c r="I20" t="n">
-        <v>2018</v>
+        <v>2021</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.8937835684963534</v>
+        <v>0.2156</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.05961553392826621</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>43830</v>
+        <v>44926</v>
       </c>
       <c r="C21" t="n">
-        <v>1547.04</v>
+        <v>1704.63</v>
       </c>
       <c r="D21" t="n">
-        <v>350.57</v>
+        <v>-164.99</v>
       </c>
       <c r="E21" t="n">
-        <v>0.293003585547485</v>
+        <v>-0.0882478792481894</v>
       </c>
       <c r="F21" t="n">
-        <v>1189.04</v>
+        <v>1873.04</v>
       </c>
       <c r="G21" t="n">
-        <v>1170.69</v>
+        <v>1456.38</v>
       </c>
       <c r="H21" t="n">
-        <v>1567.61</v>
+        <v>1913.01</v>
       </c>
       <c r="I21" t="n">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="J21" t="n">
-        <v>1.257517899414159</v>
+        <v>-0.0924</v>
+      </c>
+      <c r="K21" t="n">
+        <v>-1.454120943112114</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>44196</v>
+        <v>45291</v>
       </c>
       <c r="C22" t="n">
-        <v>1506.95</v>
+        <v>2099.78</v>
       </c>
       <c r="D22" t="n">
-        <v>-40.0899999999999</v>
+        <v>395.15</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.0259140035163925</v>
+        <v>0.231809835565489</v>
       </c>
       <c r="F22" t="n">
-        <v>1550.8</v>
+        <v>1709.71</v>
       </c>
       <c r="G22" t="n">
-        <v>954.55</v>
+        <v>1709.71</v>
       </c>
       <c r="H22" t="n">
-        <v>1602.32</v>
+        <v>2133.06</v>
       </c>
       <c r="I22" t="n">
-        <v>2020</v>
+        <v>2023</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.4344642318556678</v>
+        <v>0.2085</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.0247209592951924</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="C23" t="n">
-        <v>1869.62</v>
+        <v>2349</v>
       </c>
       <c r="D23" t="n">
-        <v>362.67</v>
+        <v>249.22</v>
       </c>
       <c r="E23" t="n">
-        <v>0.240664919207671</v>
+        <v>0.118688624522569</v>
       </c>
       <c r="F23" t="n">
-        <v>1513.51</v>
+        <v>2104.21</v>
       </c>
       <c r="G23" t="n">
-        <v>1475.91</v>
+        <v>2036.63</v>
       </c>
       <c r="H23" t="n">
-        <v>1918.65</v>
+        <v>2424.75</v>
       </c>
       <c r="I23" t="n">
-        <v>2021</v>
+        <v>2024</v>
       </c>
       <c r="J23" t="n">
-        <v>0.9798408716860909</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="B24" s="2" t="n">
-        <v>44926</v>
-      </c>
-      <c r="C24" t="n">
-        <v>1704.63</v>
-      </c>
-      <c r="D24" t="n">
-        <v>-164.99</v>
-      </c>
-      <c r="E24" t="n">
-        <v>-0.0882478792481894</v>
-      </c>
-      <c r="F24" t="n">
-        <v>1873.04</v>
-      </c>
-      <c r="G24" t="n">
-        <v>1456.38</v>
-      </c>
-      <c r="H24" t="n">
-        <v>1913.01</v>
-      </c>
-      <c r="I24" t="n">
-        <v>2022</v>
-      </c>
-      <c r="J24" t="n">
-        <v>-0.7651697417667866</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="B25" s="2" t="n">
-        <v>45291</v>
-      </c>
-      <c r="C25" t="n">
-        <v>2099.78</v>
-      </c>
-      <c r="D25" t="n">
-        <v>395.15</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0.231809835565489</v>
-      </c>
-      <c r="F25" t="n">
-        <v>1709.71</v>
-      </c>
-      <c r="G25" t="n">
-        <v>1709.71</v>
-      </c>
-      <c r="H25" t="n">
-        <v>2133.06</v>
-      </c>
-      <c r="I25" t="n">
-        <v>2023</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0.9328612010525258</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="B26" s="2" t="n">
-        <v>45657</v>
-      </c>
-      <c r="C26" t="n">
-        <v>2349</v>
-      </c>
-      <c r="D26" t="n">
-        <v>249.22</v>
-      </c>
-      <c r="E26" t="n">
-        <v>0.118688624522569</v>
-      </c>
-      <c r="F26" t="n">
-        <v>2104.21</v>
-      </c>
-      <c r="G26" t="n">
-        <v>2036.63</v>
-      </c>
-      <c r="H26" t="n">
-        <v>2424.75</v>
-      </c>
-      <c r="I26" t="n">
-        <v>2024</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0.3327090792644502</v>
+        <v>0.1122</v>
+      </c>
+      <c r="K23" t="n">
+        <v>-0.4485674262210044</v>
       </c>
     </row>
   </sheetData>
